--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0D4D907-0555-4143-AA32-4BAC704F85D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F45B01-2A7D-4DA6-99C4-4F0FC1D7EE3C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CABFD1A2-1065-44DA-8769-DC9B4324A7D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCAB195E-E2F6-4978-AF0D-3B41F8A9B39E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{410DF0D9-2CE3-4BDD-8868-712BA8E73FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AAB8873-6A2C-47FC-A67A-6669DAE75CA4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59F45B01-2A7D-4DA6-99C4-4F0FC1D7EE3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C2BB4B1-4F0D-4DE1-A35C-A8D32203EA4F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCAB195E-E2F6-4978-AF0D-3B41F8A9B39E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B83949B-BB5E-4D77-8589-310940D637AD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AAB8873-6A2C-47FC-A67A-6669DAE75CA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AA7B508-5F42-4C5B-953C-603B768EA0DD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C2BB4B1-4F0D-4DE1-A35C-A8D32203EA4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9955847-804C-44E3-A73F-9AE3DB8E5496}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B83949B-BB5E-4D77-8589-310940D637AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59C94112-CD20-44BC-953F-E2E0FBFD85AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AA7B508-5F42-4C5B-953C-603B768EA0DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27E28601-36CD-4C6B-BCDE-BB4942DE7F8E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9955847-804C-44E3-A73F-9AE3DB8E5496}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B8A107F-63A9-49C5-9FFF-99E573B058E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59C94112-CD20-44BC-953F-E2E0FBFD85AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9A4E78-B345-4D0F-9DC5-12734137E1AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27E28601-36CD-4C6B-BCDE-BB4942DE7F8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E3B9282-3915-4915-B529-384E26FFD193}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -11,6 +11,116 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Dexterity</t>
+  </si>
+  <si>
+    <t>Ateles ater</t>
+  </si>
+  <si>
+    <t>Canis latrans</t>
+  </si>
+  <si>
+    <t>Canis familiaris</t>
+  </si>
+  <si>
+    <t>Capra hircus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Cebus apella</t>
+  </si>
+  <si>
+    <t>Chlorocebus sabaeus</t>
+  </si>
+  <si>
+    <t>Cercopithecus pygerythrus</t>
+  </si>
+  <si>
+    <t>Dasypus novemcinctus</t>
+  </si>
+  <si>
+    <t>Didelphis virginiana</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Felis domesticus</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Galago crassicaudatus</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Myocastor coypus</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Potorous tridactylus</t>
+  </si>
+  <si>
+    <t>Potos flavus</t>
+  </si>
+  <si>
+    <t>Procyon lotor</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saimiri boliviensis boliviensis</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Setonix brachyurus</t>
+  </si>
+  <si>
+    <t>Trichosurus vulpecula</t>
+  </si>
+  <si>
+    <t>Tupaia belangeri</t>
+  </si>
+  <si>
+    <t>Tupaia glis</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,328 +464,248 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dexterity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ateles ater</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Canis latrans</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Canis familiaris</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Capra hircus</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Cebus apella</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cercopithecus pygerythrus</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Didelphis virginiana</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Felis domesticus</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Galago crassicaudatus</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
       </c>
       <c r="C11">
         <v>7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>19</v>
       </c>
       <c r="C13">
         <v>5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Myocastor coypus</t>
-        </is>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>21</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>22</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Potorous tridactylus</t>
-        </is>
+    <row r="18" spans="1:3">
+      <c r="B18" t="s">
+        <v>24</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Potos flavus</t>
-        </is>
+    <row r="19" spans="1:3">
+      <c r="B19" t="s">
+        <v>25</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Procyon lotor</t>
-        </is>
+    <row r="20" spans="1:3">
+      <c r="B20" t="s">
+        <v>26</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+    <row r="22" spans="1:3">
+      <c r="B22" t="s">
+        <v>28</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis boliviensis</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
       </c>
       <c r="C23">
         <v>5</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Setonix brachyurus</t>
-        </is>
+    <row r="24" spans="1:3">
+      <c r="B24" t="s">
+        <v>31</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Trichosurus vulpecula</t>
-        </is>
+    <row r="25" spans="1:3">
+      <c r="B25" t="s">
+        <v>32</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tupaia belangeri</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tupaia glis</t>
-        </is>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -962,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B8A107F-63A9-49C5-9FFF-99E573B058E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4CC54EC-6069-4B0D-B25E-348E5F165851}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9A4E78-B345-4D0F-9DC5-12734137E1AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DDED7B-109D-4962-9B27-C931ACF7209E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E3B9282-3915-4915-B529-384E26FFD193}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8E80A0-5C09-4C1A-81D9-DD33C7B03B13}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4CC54EC-6069-4B0D-B25E-348E5F165851}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D34E360A-B1C1-4DD9-868F-8853ED606BFA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DDED7B-109D-4962-9B27-C931ACF7209E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1024156A-64BA-4621-9168-85E08315A3B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB8E80A0-5C09-4C1A-81D9-DD33C7B03B13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71DD66E4-4AA4-440C-8371-1528B1D4654A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D34E360A-B1C1-4DD9-868F-8853ED606BFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E11445F8-01EF-448B-8C5E-9A49D5ECFC2B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1024156A-64BA-4621-9168-85E08315A3B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{091478CB-C0FA-4DFD-B638-609D1E0DE7DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71DD66E4-4AA4-440C-8371-1528B1D4654A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A8456D9-8AB6-493C-ADDF-75325375E5FF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,291 +714,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E11445F8-01EF-448B-8C5E-9A49D5ECFC2B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{091478CB-C0FA-4DFD-B638-609D1E0DE7DA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A8456D9-8AB6-493C-ADDF-75325375E5FF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,4 +714,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D8953E-5AE8-4814-A899-790FC6F07AED}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E2EC097-7B11-47DE-9B2F-E8504DEA8B21}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{712CA434-0F7F-4499-B3C4-4AEEBB12C6F9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,291 +714,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D8953E-5AE8-4814-A899-790FC6F07AED}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E2EC097-7B11-47DE-9B2F-E8504DEA8B21}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{712CA434-0F7F-4499-B3C4-4AEEBB12C6F9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,4 +714,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEB5BDDF-5305-4C08-AE24-22F6BEA83F2B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7195B9-B479-4002-9221-5A5F9D705CA1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6FCDE84-F39A-4E70-90EC-DE31AEE3B2F0}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEB5BDDF-5305-4C08-AE24-22F6BEA83F2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1362588E-18CE-4067-BA82-6E34E89EEBCB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7195B9-B479-4002-9221-5A5F9D705CA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D2A30F2-DDD0-4389-9C48-D41D99650996}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6FCDE84-F39A-4E70-90EC-DE31AEE3B2F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D2789B-1088-4D96-95B7-0110B84908A9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1362588E-18CE-4067-BA82-6E34E89EEBCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED45234-7EEC-4B71-9B06-FBDF056B0F47}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D2A30F2-DDD0-4389-9C48-D41D99650996}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6DA05DA-782C-438C-A3BF-F80AB1AEA1CE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D2789B-1088-4D96-95B7-0110B84908A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55D34925-6770-4F36-AF82-F8D38E7188EE}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED45234-7EEC-4B71-9B06-FBDF056B0F47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF1FD197-6FA2-4668-852D-AE2E71118F30}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6DA05DA-782C-438C-A3BF-F80AB1AEA1CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10A9781-05F7-450A-9488-6E2488F553EE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55D34925-6770-4F36-AF82-F8D38E7188EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105D150C-24D8-4174-8663-0F9574865E90}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF1FD197-6FA2-4668-852D-AE2E71118F30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF8A408-9AFB-42C4-898B-EC6577934ED2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B10A9781-05F7-450A-9488-6E2488F553EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88918DAA-CBC9-4F96-80BF-5CF08D954661}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105D150C-24D8-4174-8663-0F9574865E90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BAD8EFF-5CF0-45A0-B7B7-475E51B25AA2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF8A408-9AFB-42C4-898B-EC6577934ED2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF47D109-A6A5-49FD-8FC4-342AFFEEF310}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88918DAA-CBC9-4F96-80BF-5CF08D954661}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A99DD85-6C4A-4AEE-92AD-E3B81585FC9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BAD8EFF-5CF0-45A0-B7B7-475E51B25AA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4870B4EA-DFA7-42F5-9D9B-0E1D8CB9C370}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,291 +714,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF47D109-A6A5-49FD-8FC4-342AFFEEF310}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A99DD85-6C4A-4AEE-92AD-E3B81585FC9E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4870B4EA-DFA7-42F5-9D9B-0E1D8CB9C370}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,4 +714,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2E0524-D8B9-4FD0-94F5-E6307619B4E7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{798552CE-EADE-4F37-A818-A2F18ADBBCD0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21032CB3-1726-4366-A821-CA760B0AE896}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2E0524-D8B9-4FD0-94F5-E6307619B4E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDB76FF-FD19-42BA-A609-CA275F3D8183}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{798552CE-EADE-4F37-A818-A2F18ADBBCD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A30084-2AF4-4559-BE29-30858795CA86}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21032CB3-1726-4366-A821-CA760B0AE896}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CDEC63-0E42-42FD-9911-FD724E5CF4DA}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECDB76FF-FD19-42BA-A609-CA275F3D8183}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60BB6E2C-34AF-4C6B-BA34-1796EFD22653}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6A30084-2AF4-4559-BE29-30858795CA86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74463CA-1CA8-466A-84AD-968169E0DCF7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37CDEC63-0E42-42FD-9911-FD724E5CF4DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1791652-6150-4922-8983-9A67C65180D2}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60BB6E2C-34AF-4C6B-BA34-1796EFD22653}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77927ECB-007B-45AF-80FF-3AC3E723F94E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E74463CA-1CA8-466A-84AD-968169E0DCF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7AA0A2-72BC-4301-B147-3CD36EEB819C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1791652-6150-4922-8983-9A67C65180D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F34646E4-D28C-4127-B1D5-6C8329712CD1}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77927ECB-007B-45AF-80FF-3AC3E723F94E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EAA5A8-B027-42FB-8B17-1D2D932A7BC7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7AA0A2-72BC-4301-B147-3CD36EEB819C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D051880E-848C-4307-A393-B7DB2836F260}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F34646E4-D28C-4127-B1D5-6C8329712CD1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0EEBE7-852A-43A8-BCAF-77C301F20942}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -992,13 +992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EAA5A8-B027-42FB-8B17-1D2D932A7BC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42F6E241-9BA5-4B92-9E27-417CBA3866B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D051880E-848C-4307-A393-B7DB2836F260}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2951217B-9026-4CBE-8783-D30FE64884A8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0EEBE7-852A-43A8-BCAF-77C301F20942}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B0BE23-E2DE-45A3-8AE3-7C55EC2C6F03}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,291 +714,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42F6E241-9BA5-4B92-9E27-417CBA3866B9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2951217B-9026-4CBE-8783-D30FE64884A8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B0BE23-E2DE-45A3-8AE3-7C55EC2C6F03}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -714,4 +714,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{143CC1C7-A621-40FB-8ED5-4436DCE7390E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C79E404-F22E-456E-9A92-5C810B549900}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1208AF1C-4CB6-4E3B-9B11-07C4C572D9F7}"/>
 </file>